--- a/artfynd/A 13640-2026 artfynd.xlsx
+++ b/artfynd/A 13640-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>91279038</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97986</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
